--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_30.xlsx
@@ -1,67 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{58F35B26-4AD7-4B95-87E6-8F399A9E6CE6}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB5BB97-C2FF-4F73-83C7-E9996EF12949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="16" firstSheet="15" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PayNowNoCFCorp" r:id="rId1" sheetId="1"/>
-    <sheet name="PayNowNoCFPC" r:id="rId2" sheetId="2"/>
-    <sheet name="PayNowNoCFPS" r:id="rId3" sheetId="3"/>
-    <sheet name="PayNowSCFCorp" r:id="rId4" sheetId="4"/>
-    <sheet name="PayNowSCFPC" r:id="rId5" sheetId="5"/>
-    <sheet name="PayNowSCFPS" r:id="rId6" sheetId="6"/>
-    <sheet name="PayNowDCFPC" r:id="rId7" sheetId="7"/>
-    <sheet name="PayNowDCFCorp" r:id="rId8" sheetId="45"/>
-    <sheet name="PayNowDCFPS" r:id="rId9" sheetId="8"/>
-    <sheet name="NoModifyAmountCorp" r:id="rId10" sheetId="9"/>
-    <sheet name="NoModifyAmountPC" r:id="rId11" sheetId="10"/>
-    <sheet name="NoModifyAmountPS" r:id="rId12" sheetId="11"/>
-    <sheet name="NoModifyBillingAddressCorp" r:id="rId13" sheetId="12"/>
-    <sheet name="NoModifyBillingAddressPC" r:id="rId14" sheetId="13"/>
-    <sheet name="NoModifyBillingAddressPS" r:id="rId15" sheetId="14"/>
-    <sheet name="VerifyPaymentReceiptCorp" r:id="rId16" sheetId="15"/>
-    <sheet name="VerifyPaymentReceiptPC" r:id="rId17" sheetId="16"/>
-    <sheet name="SCFCorpVerbiage" r:id="rId18" sheetId="17"/>
-    <sheet name="DCFCorpVerbiage" r:id="rId19" sheetId="20"/>
-    <sheet name="SCFPCVerbiage" r:id="rId20" sheetId="18"/>
-    <sheet name="DCFPCVerbiage" r:id="rId21" sheetId="21"/>
-    <sheet name="DCFPSVerbiage" r:id="rId22" sheetId="22"/>
-    <sheet name="CMCAutopayCorp" r:id="rId23" sheetId="23"/>
-    <sheet name="CMCAutopayPC" r:id="rId24" sheetId="24"/>
-    <sheet name="CMCAutopayPS" r:id="rId25" sheetId="25"/>
-    <sheet name="CMCDeferredCorp" r:id="rId26" sheetId="26"/>
-    <sheet name="CMCDeferredPC" r:id="rId27" sheetId="27"/>
-    <sheet name="CMCDeferredPS" r:id="rId28" sheetId="28"/>
-    <sheet name="CancelStaticTextAutopayCorp" r:id="rId29" sheetId="29"/>
-    <sheet name="CancelSuccessAutopayCorp" r:id="rId30" sheetId="30"/>
-    <sheet name="ModifyStaticTextAutopayCorp" r:id="rId31" sheetId="31"/>
-    <sheet name="ModifySuccessAutopayCorp" r:id="rId32" sheetId="32"/>
-    <sheet name="CancelStaticTextAutopayPC" r:id="rId33" sheetId="33"/>
-    <sheet name="CancelSuccessAutopayPC" r:id="rId34" sheetId="34"/>
-    <sheet name="ModifyStaticTextAutopayPC" r:id="rId35" sheetId="35"/>
-    <sheet name="ModifySuccessAutopayPC" r:id="rId36" sheetId="36"/>
-    <sheet name="CancelStaticTextDeferredCorp" r:id="rId37" sheetId="37"/>
-    <sheet name="CancelSuccessDeferredCorp" r:id="rId38" sheetId="38"/>
-    <sheet name="ModifyStaticTextDeferredCorp" r:id="rId39" sheetId="39"/>
-    <sheet name="CancelStaticTextDeferredPC" r:id="rId40" sheetId="41"/>
-    <sheet name="ModifyStaticTextDeferredPC" r:id="rId41" sheetId="43"/>
-    <sheet name="ModifySuccessDeferredPC" r:id="rId42" sheetId="44"/>
-    <sheet name="CancelSuccessDeferredPC" r:id="rId43" sheetId="42"/>
-    <sheet name="ModifySuccessDeferredCorp" r:id="rId44" sheetId="40"/>
-    <sheet name="SCFPSVerbiage" r:id="rId45" sheetId="19"/>
+    <sheet name="PayNowNoCFCorp" sheetId="1" r:id="rId1"/>
+    <sheet name="PayNowNoCFPC" sheetId="2" r:id="rId2"/>
+    <sheet name="PayNowNoCFPS" sheetId="3" r:id="rId3"/>
+    <sheet name="PayNowSCFCorp" sheetId="4" r:id="rId4"/>
+    <sheet name="PayNowSCFPC" sheetId="5" r:id="rId5"/>
+    <sheet name="PayNowSCFPS" sheetId="6" r:id="rId6"/>
+    <sheet name="PayNowDCFPC" sheetId="7" r:id="rId7"/>
+    <sheet name="PayNowDCFCorp" sheetId="45" r:id="rId8"/>
+    <sheet name="PayNowDCFPS" sheetId="8" r:id="rId9"/>
+    <sheet name="NoModifyAmountCorp" sheetId="9" r:id="rId10"/>
+    <sheet name="NoModifyAmountPC" sheetId="10" r:id="rId11"/>
+    <sheet name="NoModifyAmountPS" sheetId="11" r:id="rId12"/>
+    <sheet name="NoModifyBillingAddressCorp" sheetId="12" r:id="rId13"/>
+    <sheet name="NoModifyBillingAddressPC" sheetId="13" r:id="rId14"/>
+    <sheet name="NoModifyBillingAddressPS" sheetId="14" r:id="rId15"/>
+    <sheet name="VerifyPaymentReceiptCorp" sheetId="15" r:id="rId16"/>
+    <sheet name="VerifyPaymentReceiptPC" sheetId="16" r:id="rId17"/>
+    <sheet name="SCFCorpVerbiage" sheetId="17" r:id="rId18"/>
+    <sheet name="DCFCorpVerbiage" sheetId="20" r:id="rId19"/>
+    <sheet name="SCFPCVerbiage" sheetId="18" r:id="rId20"/>
+    <sheet name="DCFPCVerbiage" sheetId="21" r:id="rId21"/>
+    <sheet name="DCFPSVerbiage" sheetId="22" r:id="rId22"/>
+    <sheet name="CMCAutopayCorp" sheetId="23" r:id="rId23"/>
+    <sheet name="CMCAutopayPC" sheetId="24" r:id="rId24"/>
+    <sheet name="CMCAutopayPS" sheetId="25" r:id="rId25"/>
+    <sheet name="CMCDeferredCorp" sheetId="26" r:id="rId26"/>
+    <sheet name="CMCDeferredPC" sheetId="27" r:id="rId27"/>
+    <sheet name="CMCDeferredPS" sheetId="28" r:id="rId28"/>
+    <sheet name="CancelStaticTextAutopayCorp" sheetId="29" r:id="rId29"/>
+    <sheet name="CancelSuccessAutopayCorp" sheetId="30" r:id="rId30"/>
+    <sheet name="ModifyStaticTextAutopayCorp" sheetId="31" r:id="rId31"/>
+    <sheet name="ModifySuccessAutopayCorp" sheetId="32" r:id="rId32"/>
+    <sheet name="CancelStaticTextAutopayPC" sheetId="33" r:id="rId33"/>
+    <sheet name="CancelSuccessAutopayPC" sheetId="34" r:id="rId34"/>
+    <sheet name="ModifyStaticTextAutopayPC" sheetId="35" r:id="rId35"/>
+    <sheet name="ModifySuccessAutopayPC" sheetId="36" r:id="rId36"/>
+    <sheet name="CancelStaticTextDeferredCorp" sheetId="37" r:id="rId37"/>
+    <sheet name="CancelSuccessDeferredCorp" sheetId="38" r:id="rId38"/>
+    <sheet name="ModifyStaticTextDeferredCorp" sheetId="39" r:id="rId39"/>
+    <sheet name="CancelStaticTextDeferredPC" sheetId="41" r:id="rId40"/>
+    <sheet name="ModifyStaticTextDeferredPC" sheetId="43" r:id="rId41"/>
+    <sheet name="ModifySuccessDeferredPC" sheetId="44" r:id="rId42"/>
+    <sheet name="CancelSuccessDeferredPC" sheetId="42" r:id="rId43"/>
+    <sheet name="ModifySuccessDeferredCorp" sheetId="40" r:id="rId44"/>
+    <sheet name="SCFPSVerbiage" sheetId="19" r:id="rId45"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="70">
   <si>
     <t>Result</t>
   </si>
@@ -140,9 +140,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <t>985</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>18</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
     <t>12/31/2026</t>
   </si>
   <si>
@@ -167,273 +161,12 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Tue May 05 21:54:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:05:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:06:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:08:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:13:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:14:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:15:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:17:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:18:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:19:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:21:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:23:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:24:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:26:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:27:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:28:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:30:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:31:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:32:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:36:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:43:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 22:55:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:01:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:18:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:41:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:42:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:43:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:44:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:48:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:50:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:53:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 23:55:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 00:39:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 00:56:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 00:58:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 20:26:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 20:30:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 20:41:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 21:30:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 21:45:34 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed May 06 21:51:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:50:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:52:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:54:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:01:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:02:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:03:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:04:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:06:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:07:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:08:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:10:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:11:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:12:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:14:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:15:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:18:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:19:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:20:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:22:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:24:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:25:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:27:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:28:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:29:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:31:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:33:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:34:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:36:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:37:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:38:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:44:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:46:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:48:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:50:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:52:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:54:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:56:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:57:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:06:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:08:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:10:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:17:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:19:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 00:23:21 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Jun 06 00:38:39 IST 2026</t>
   </si>
   <si>
     <t>Sat Jun 06 00:46:08 IST 2026</t>
   </si>
   <si>
-    <t>Sat Jun 06 00:49:06 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Jun 06 00:49:52 IST 2026</t>
   </si>
   <si>
@@ -449,27 +182,9 @@
     <t>Sat Jun 06 00:57:09 IST 2026</t>
   </si>
   <si>
-    <t>Sat Jun 06 01:03:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 01:04:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 01:05:58 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Jun 06 01:07:21 IST 2026</t>
   </si>
   <si>
-    <t>Sat Jun 06 01:14:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 01:16:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 01:17:55 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Jun 06 01:19:11 IST 2026</t>
   </si>
   <si>
@@ -485,14 +200,91 @@
     <t>Sat Jun 06 01:29:49 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jun 08 19:25:32 IST 2026</t>
+    <t>Wed Aug 19 08:14:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 08:15:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 08:17:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 09:11:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 09:12:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 09:13:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 09:58:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 10:05:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 10:50:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 10:52:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 11:40:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 11:42:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 10:21:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 10:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 10:26:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:14:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:16:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:19:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:20:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:21:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 11:26:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 12:20:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 12:21:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 12:23:17 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -535,21 +327,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -566,10 +358,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -604,7 +396,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -639,7 +431,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -733,21 +525,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -764,7 +556,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -816,18 +608,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,10 +665,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -912,16 +704,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2443937-441A-4235-918C-DDBF3FD83D3F}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2443937-441A-4235-918C-DDBF3FD83D3F}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,10 +759,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -980,7 +772,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1004,19 +796,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB6AB9-866B-41DE-9360-3C38CC6DDDC7}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB6AB9-866B-41DE-9360-3C38CC6DDDC7}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,10 +854,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1075,7 +867,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1099,16 +891,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22E15AE-B339-4793-93AB-EB5A79E85E9A}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22E15AE-B339-4793-93AB-EB5A79E85E9A}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1154,10 +946,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1167,7 +959,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1191,16 +983,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671DDEC9-65DE-400C-8C3C-5EA1418D698B}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671DDEC9-65DE-400C-8C3C-5EA1418D698B}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1246,10 +1038,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1259,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1283,16 +1075,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB09C1B1-3ED0-46FB-B187-E5D4FEDAB59D}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB09C1B1-3ED0-46FB-B187-E5D4FEDAB59D}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,10 +1130,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1351,7 +1143,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1375,16 +1167,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CC597F-30CA-472D-89B3-F7E3EC35F6CC}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CC597F-30CA-472D-89B3-F7E3EC35F6CC}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1430,10 +1222,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1443,7 +1235,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1467,16 +1259,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB3E83E-D8F5-4824-88EE-2F0ADFE067EF}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB3E83E-D8F5-4824-88EE-2F0ADFE067EF}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1522,10 +1314,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1561,19 +1353,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8210E3-2DA1-4A15-8B16-56DCA80116AC}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8210E3-2DA1-4A15-8B16-56DCA80116AC}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,10 +1411,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1658,16 +1450,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07329C66-2323-4D03-B970-8CA4C1E61984}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07329C66-2323-4D03-B970-8CA4C1E61984}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1713,10 +1505,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1726,7 +1518,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1752,16 +1544,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1428B345-D03E-4D53-8E6F-BE1455504E17}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1428B345-D03E-4D53-8E6F-BE1455504E17}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1807,10 +1599,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1820,7 +1612,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1846,19 +1638,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C767928-AB4C-45C4-8182-4D126CDFFE78}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C767928-AB4C-45C4-8182-4D126CDFFE78}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1904,10 +1696,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1943,16 +1735,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B9D9D5-6BF3-4F10-8EC1-02827FA051C6}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B9D9D5-6BF3-4F10-8EC1-02827FA051C6}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1998,10 +1790,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2011,7 +1803,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2037,16 +1829,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AADD4C-D259-4CE6-8578-D97B6C2F8B10}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AADD4C-D259-4CE6-8578-D97B6C2F8B10}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2096,7 +1888,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -2125,16 +1917,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EC88A9-1BE3-4163-8C3B-AD05BE1445BB}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EC88A9-1BE3-4163-8C3B-AD05BE1445BB}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2180,10 +1972,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2193,7 +1985,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2219,16 +2011,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6435C448-AD20-47DF-AF9D-DE439C813DC1}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6435C448-AD20-47DF-AF9D-DE439C813DC1}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2274,17 +2066,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -2313,19 +2105,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76C3A63-D16F-4C1B-96B2-7B82F9EC8080}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76C3A63-D16F-4C1B-96B2-7B82F9EC8080}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2371,17 +2163,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -2410,19 +2202,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07365AD8-C2C7-439C-8378-02C500A8C26D}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07365AD8-C2C7-439C-8378-02C500A8C26D}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2468,16 +2260,16 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -2506,16 +2298,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F0775D-FB6F-42B7-8CA2-B04EBD30F3F8}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F0775D-FB6F-42B7-8CA2-B04EBD30F3F8}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2559,12 +2351,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2592,7 +2384,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -2602,19 +2394,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3EB35-350B-478C-982C-A185F743C3F1}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3EB35-350B-478C-982C-A185F743C3F1}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2658,12 +2450,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2691,7 +2483,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -2701,16 +2493,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BC66D9-4F87-4753-8110-4AB5BE44C35F}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BC66D9-4F87-4753-8110-4AB5BE44C35F}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2754,12 +2546,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2787,7 +2579,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -2797,16 +2589,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33049D1A-E1EA-4158-9F11-CF5B37A15CD9}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33049D1A-E1EA-4158-9F11-CF5B37A15CD9}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2852,17 +2644,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -2891,16 +2683,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C94F67-FA9C-4C35-BDDF-8F6371A635CA}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C94F67-FA9C-4C35-BDDF-8F6371A635CA}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2946,10 +2738,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2985,16 +2777,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DBAF23-06D5-44B9-BB86-B9E819408F45}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DBAF23-06D5-44B9-BB86-B9E819408F45}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3040,17 +2832,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3079,16 +2871,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7362791-C2DC-4CDD-9264-ABD5FE69D391}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7362791-C2DC-4CDD-9264-ABD5FE69D391}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3134,17 +2926,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3173,16 +2965,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E3BA3A-35D5-4B65-AE42-C094AC4A2F39}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E3BA3A-35D5-4B65-AE42-C094AC4A2F39}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3228,17 +3020,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3267,16 +3059,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C2B334-026E-4998-B41F-E7BFFF863F81}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C2B334-026E-4998-B41F-E7BFFF863F81}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3322,17 +3114,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3361,16 +3153,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9112718D-2982-4B6B-AFC2-0660919063C6}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9112718D-2982-4B6B-AFC2-0660919063C6}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3416,17 +3208,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3455,16 +3247,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9B2098-FA65-4BDE-A685-FAC1CF5ACCA7}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9B2098-FA65-4BDE-A685-FAC1CF5ACCA7}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3510,17 +3302,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3549,13 +3341,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4829852-5AD5-41CF-A108-7321E7BCF28A}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4829852-5AD5-41CF-A108-7321E7BCF28A}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3604,17 +3396,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>119</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3643,16 +3435,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA19345A-4159-4FD9-BE1E-2071E347E245}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA19345A-4159-4FD9-BE1E-2071E347E245}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3696,12 +3488,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3729,7 +3521,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -3739,16 +3531,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FCD55C-A25C-4912-B829-FE097D1207F7}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FCD55C-A25C-4912-B829-FE097D1207F7}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3792,7 +3584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -3819,7 +3611,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -3829,25 +3621,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737EF744-D8A3-4EF5-BB52-132AB1545069}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737EF744-D8A3-4EF5-BB52-132AB1545069}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFDF9299-FF8F-4BFC-8220-D01F8C2EE400}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFDF9299-FF8F-4BFC-8220-D01F8C2EE400}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3893,10 +3685,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3906,7 +3698,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3932,16 +3724,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B75322-BAC4-43CD-AB14-2125A6576883}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B75322-BAC4-43CD-AB14-2125A6576883}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3985,12 +3777,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4018,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -4028,16 +3820,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3386F41-741B-41B0-BBF2-0854070A3164}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3386F41-741B-41B0-BBF2-0854070A3164}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4081,12 +3873,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4114,7 +3906,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -4124,16 +3916,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F08F90-4A07-46CE-AEBB-DAAF2D27242A}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F08F90-4A07-46CE-AEBB-DAAF2D27242A}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4177,12 +3969,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4210,7 +4002,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -4220,16 +4012,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037B30C9-3EB0-4E2A-9E7E-19F21CBB4542}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037B30C9-3EB0-4E2A-9E7E-19F21CBB4542}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4273,12 +4065,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4306,7 +4098,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -4316,25 +4108,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0CBAAE4-EA85-479A-B264-91C99B36FCE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0CBAAE4-EA85-479A-B264-91C99B36FCE9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92A16C3-F0C6-4205-9E33-B4EEBC3B6A9B}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92A16C3-F0C6-4205-9E33-B4EEBC3B6A9B}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4387,7 +4179,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4413,16 +4205,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB58A54-F999-4BB2-B874-8E073453B531}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB58A54-F999-4BB2-B874-8E073453B531}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4468,10 +4260,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4481,7 +4273,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4507,16 +4299,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A99629-E899-4C1F-8C81-F3E0FF4F1B75}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A99629-E899-4C1F-8C81-F3E0FF4F1B75}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4562,10 +4354,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4575,7 +4367,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4601,16 +4393,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AFF63A7-761C-4635-A654-2590A7E98D6F}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AFF63A7-761C-4635-A654-2590A7E98D6F}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4656,10 +4448,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4669,7 +4461,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4695,16 +4487,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{566BA3ED-2DFD-4D07-B454-1DBCCA89DDAF}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{566BA3ED-2DFD-4D07-B454-1DBCCA89DDAF}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4750,10 +4542,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4763,7 +4555,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4789,16 +4581,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BB6ECD-03FA-44B7-B27E-878399B01BD0}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BB6ECD-03FA-44B7-B27E-878399B01BD0}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4844,10 +4636,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4857,7 +4649,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4883,6 +4675,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_30.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
@@ -61,7 +61,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="187">
   <si>
     <t>Result</t>
   </si>
@@ -279,12 +279,364 @@
   </si>
   <si>
     <t>Thu Aug 20 12:23:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:02:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:05:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:07:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:11:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:12:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:14:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:17:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:18:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:20:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:23:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:24:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:25:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:28:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:29:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:31:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:33:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:35:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:39:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:41:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:44:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:47:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 17:58:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:00:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:02:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:14:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:17:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:19:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:28:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:32:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:41:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:50:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:53:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:54:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 18:58:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:01:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:18:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:27:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:30:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:31:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:34:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:37:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:42:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 19:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 06 20:13:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:20:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:24:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:26:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:27:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:31:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:32:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:33:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:36:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:38:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:39:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:40:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:41:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:44:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:46:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:47:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:54:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:56:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 01:58:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:00:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:01:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:05:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:08:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:10:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:11:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:14:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:19:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:23:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:24:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:26:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:29:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:31:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:40:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:42:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 02:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:03:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:06:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:09:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:19:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:24:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:25:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:27:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:30:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:37:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:43:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:55:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:57:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 03:59:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:02:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:05:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 04:08:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 20:32:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 20:39:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 20:51:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 20:58:18 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -664,11 +1016,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>43</v>
+      <c r="B2" t="s" s="0">
+        <v>146</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -758,11 +1110,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>61</v>
+      <c r="B2" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -805,7 +1157,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -853,11 +1205,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>62</v>
+      <c r="B2" t="s" s="0">
+        <v>131</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -945,11 +1297,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
+      <c r="A2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>186</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1037,11 +1389,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>64</v>
+      <c r="B2" t="s" s="0">
+        <v>136</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1129,11 +1481,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>65</v>
+      <c r="B2" t="s" s="0">
+        <v>138</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1221,11 +1573,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>66</v>
+      <c r="B2" t="s" s="0">
+        <v>139</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1313,11 +1665,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>39</v>
+      <c r="B2" t="s" s="0">
+        <v>176</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1362,7 +1714,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1410,11 +1762,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>40</v>
+      <c r="B2" t="s" s="0">
+        <v>180</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1504,11 +1856,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>41</v>
+      <c r="B2" t="s" s="0">
+        <v>181</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1598,11 +1950,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="B2" t="s" s="0">
+        <v>166</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1647,7 +1999,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1695,11 +2047,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>44</v>
+      <c r="B2" t="s" s="0">
+        <v>149</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1789,11 +2141,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
+      <c r="B2" t="s" s="0">
+        <v>182</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1971,11 +2323,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>170</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2065,11 +2417,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>55</v>
+      <c r="B2" t="s" s="0">
+        <v>121</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2114,7 +2466,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2162,11 +2514,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>56</v>
+      <c r="B2" t="s" s="0">
+        <v>122</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2211,7 +2563,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2259,13 +2611,13 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2352,11 +2704,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>58</v>
+      <c r="B2" t="s" s="0">
+        <v>124</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2403,7 +2755,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2451,11 +2803,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
+      <c r="B2" t="s" s="0">
+        <v>125</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2547,11 +2899,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>60</v>
+      <c r="B2" t="s" s="0">
+        <v>126</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2643,11 +2995,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>49</v>
+      <c r="B2" t="s" s="0">
+        <v>157</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2737,11 +3089,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>45</v>
+      <c r="B2" t="s" s="0">
+        <v>184</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2831,11 +3183,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
+      <c r="B2" t="s" s="0">
+        <v>159</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2925,11 +3277,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>53</v>
+      <c r="B2" t="s" s="0">
+        <v>161</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3019,11 +3371,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
+      <c r="A2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>164</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3113,11 +3465,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>50</v>
+      <c r="B2" t="s" s="0">
+        <v>158</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3207,11 +3559,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>52</v>
+      <c r="B2" t="s" s="0">
+        <v>160</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3301,11 +3653,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>54</v>
+      <c r="B2" t="s" s="0">
+        <v>185</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3395,11 +3747,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
+      <c r="B2" t="s" s="0">
+        <v>165</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3489,11 +3841,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
+      <c r="B2" t="s" s="0">
+        <v>171</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3684,11 +4036,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>46</v>
+      <c r="B2" t="s" s="0">
+        <v>154</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3778,11 +4130,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
+      <c r="B2" t="s" s="0">
+        <v>172</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3874,11 +4226,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
+      <c r="B2" t="s" s="0">
+        <v>174</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3970,11 +4322,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>38</v>
+      <c r="B2" t="s" s="0">
+        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4066,11 +4418,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>36</v>
+      <c r="B2" t="s" s="0">
+        <v>173</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4259,11 +4611,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
+      <c r="B2" t="s" s="0">
+        <v>155</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4353,11 +4705,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
+      <c r="B2" t="s" s="0">
+        <v>156</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4447,11 +4799,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>68</v>
+      <c r="B2" t="s" s="0">
+        <v>144</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4541,11 +4893,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>67</v>
+      <c r="B2" t="s" s="0">
+        <v>142</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4635,11 +4987,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
-        <v>69</v>
+      <c r="B2" t="s" s="0">
+        <v>145</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
